--- a/排课结果/调课失败的排课失败课程.xlsx
+++ b/排课结果/调课失败的排课失败课程.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B241"/>
+  <dimension ref="A1:B232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,7 +791,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>150000290.135</t>
+          <t>150000290.215</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>150000290.160</t>
+          <t>150000290.216</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>150000290.180</t>
+          <t>150000290.217</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>150000290.215</t>
+          <t>150000290.222</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>150000290.216</t>
+          <t>150000290.223</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>150000290.217</t>
+          <t>150000290.224</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>150000290.218</t>
+          <t>150000290.225</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>150000290.221</t>
+          <t>150000290.227</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -887,91 +887,91 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>150000290.222</t>
+          <t>150130781.001</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>体育赛事组织与管理</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>150000290.223</t>
+          <t>15200002.014</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>体育与健康2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>150000290.224</t>
+          <t>15200002.015</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>体育与健康2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>150000290.225</t>
+          <t>15200002.016</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>体育与健康2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>150000290.227</t>
+          <t>15200002.018</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>体育与健康2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>150130781.001</t>
+          <t>15200002.019</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>体育赛事组织与管理</t>
+          <t>体育与健康2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>151130890.001</t>
+          <t>15200002.020</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>体育基本理论</t>
+          <t>体育与健康2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15200002.009</t>
+          <t>15200002.021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15200002.014</t>
+          <t>15200002.022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -995,7 +995,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15200002.015</t>
+          <t>15200002.023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1007,7 +1007,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15200002.016</t>
+          <t>15200002.024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15200002.018</t>
+          <t>15200002.025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>15200002.019</t>
+          <t>15200002.026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1043,7 +1043,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>15200002.020</t>
+          <t>15200002.028</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>15200002.021</t>
+          <t>15200002.029</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>15200002.022</t>
+          <t>15200002.032</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>15200002.023</t>
+          <t>15200002.033</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>15200002.024</t>
+          <t>15200002.034</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15200002.025</t>
+          <t>15200002.035</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>15200002.026</t>
+          <t>15200002.036</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>15200002.028</t>
+          <t>15200002.038</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>15200002.029</t>
+          <t>15200002.039</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>15200002.032</t>
+          <t>15200002.040</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>15200002.033</t>
+          <t>15200002.041</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>15200002.034</t>
+          <t>15200002.042</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>15200002.035</t>
+          <t>15200002.043</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>15200002.036</t>
+          <t>15200002.045</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>15200002.038</t>
+          <t>15200002.046</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>15200002.039</t>
+          <t>15200002.047</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>15200002.040</t>
+          <t>15200002.048</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>15200002.041</t>
+          <t>15200002.049</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>15200002.042</t>
+          <t>15200002.050</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>15200002.043</t>
+          <t>15200002.051</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>15200002.045</t>
+          <t>15200002.052</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>15200002.046</t>
+          <t>15200002.053</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>15200002.047</t>
+          <t>15200002.055</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>15200002.048</t>
+          <t>15200002.056</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>15200002.049</t>
+          <t>15200002.057</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>15200002.050</t>
+          <t>15200002.058</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>15200002.051</t>
+          <t>15200002.059</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>15200002.052</t>
+          <t>15200002.060</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>15200002.053</t>
+          <t>15200002.061</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>15200002.055</t>
+          <t>15200002.062</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>15200002.056</t>
+          <t>15200002.063</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>15200002.057</t>
+          <t>15200002.064</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>15200002.058</t>
+          <t>15200002.065</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>15200002.059</t>
+          <t>15200002.066</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>15200002.060</t>
+          <t>15200002.087</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>15200002.061</t>
+          <t>15200002.088</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>15200002.062</t>
+          <t>15200002.089</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>15200002.063</t>
+          <t>15200002.090</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>15200002.064</t>
+          <t>15200002.091</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>15200002.065</t>
+          <t>15200002.092</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>15200002.066</t>
+          <t>15200002.093</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1535,7 +1535,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>15200002.084</t>
+          <t>15200002.094</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>15200002.086</t>
+          <t>15200002.095</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>15200002.087</t>
+          <t>15200002.096</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>15200002.088</t>
+          <t>15200002.097</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1583,7 +1583,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>15200002.089</t>
+          <t>15200002.098</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>15200002.090</t>
+          <t>15200002.099</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>15200002.091</t>
+          <t>15200002.100</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>15200002.092</t>
+          <t>15200002.101</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>15200002.093</t>
+          <t>15200002.102</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>15200002.094</t>
+          <t>15200002.103</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>15200002.095</t>
+          <t>15200002.104</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1667,7 +1667,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>15200002.096</t>
+          <t>15200002.105</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>15200002.097</t>
+          <t>15200002.106</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -1691,7 +1691,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>15200002.098</t>
+          <t>15200002.113</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>15200002.099</t>
+          <t>15200002.123</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -1715,7 +1715,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>15200002.100</t>
+          <t>15200002.124</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -1727,7 +1727,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15200002.101</t>
+          <t>15200002.125</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>15200002.102</t>
+          <t>15200002.126</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>15200002.103</t>
+          <t>15200002.127</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -1763,7 +1763,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>15200002.104</t>
+          <t>15200002.128</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -1775,7 +1775,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>15200002.105</t>
+          <t>15200002.129</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -1787,7 +1787,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>15200002.106</t>
+          <t>15200002.130</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>15200002.113</t>
+          <t>15200002.131</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>15200002.123</t>
+          <t>15200002.132</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>15200002.124</t>
+          <t>15200002.133</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>15200002.125</t>
+          <t>15200002.134</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>15200002.126</t>
+          <t>15200002.135</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>15200002.127</t>
+          <t>15200002.136</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -1871,1438 +1871,1330 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>15200002.128</t>
+          <t>141000041.001</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>体育与健康2</t>
+          <t>大学英语提高</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>15200002.129</t>
+          <t>14403009.001</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>体育与健康2</t>
+          <t>商务英语</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>15200002.130</t>
+          <t>110000320.001</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>体育与健康2</t>
+          <t>线性代数b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>15200002.131</t>
+          <t>110000460.001</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>体育与健康2</t>
+          <t>高等数学b-2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>15200002.132</t>
+          <t>110000460.002</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>体育与健康2</t>
+          <t>高等数学b-2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>15200002.133</t>
+          <t>110000460.003</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>体育与健康2</t>
+          <t>高等数学b-2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>15200002.134</t>
+          <t>110000460.004</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>体育与健康2</t>
+          <t>高等数学b-2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>15200002.135</t>
+          <t>110000460.005</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>体育与健康2</t>
+          <t>高等数学b-2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>15200002.136</t>
+          <t>110000460.006</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>体育与健康2</t>
+          <t>高等数学b-2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>141000041.001</t>
+          <t>110000480.001</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>大学英语提高</t>
+          <t>高等数学c-2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>14403009.001</t>
+          <t>110000480.002</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>商务英语</t>
+          <t>高等数学c-2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>110000320.001</t>
+          <t>110000640.017</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>线性代数b</t>
+          <t>概率论与数理统计</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>110000460.001</t>
+          <t>110000670.001</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>高等数学b-2</t>
+          <t>高等数学a-2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>110000460.002</t>
+          <t>110000670.002</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>高等数学b-2</t>
+          <t>高等数学a-2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>110000460.003</t>
+          <t>091000021.001</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>高等数学b-2</t>
+          <t>网页设计基础</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>110000460.004</t>
+          <t>121000111.004</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>高等数学b-2</t>
+          <t>社会主义发展史</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>110000460.005</t>
+          <t>121000121.001</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>高等数学b-2</t>
+          <t>大学生职业软技能实训课程</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>110000460.006</t>
+          <t>130000510.002</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>高等数学b-2</t>
+          <t>大学物理（一）</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>110000480.001</t>
+          <t>130000510.004</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>高等数学c-2</t>
+          <t>大学物理（一）</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>110000480.002</t>
+          <t>130000510.005</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>高等数学c-2</t>
+          <t>大学物理（一）</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>110000640.017</t>
+          <t>130000510.006</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>概率论与数理统计</t>
+          <t>大学物理（一）</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>110000670.001</t>
+          <t>130000510.007</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>高等数学a-2</t>
+          <t>大学物理（一）</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>110000670.002</t>
+          <t>130000510.008</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>高等数学a-2</t>
+          <t>大学物理（一）</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>091000021.001</t>
+          <t>130000510.009</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>网页设计基础</t>
+          <t>大学物理（一）</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>121000111.004</t>
+          <t>130000510.010</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>社会主义发展史</t>
+          <t>大学物理（一）</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>121000121.001</t>
+          <t>14200002.006</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>大学生职业软技能实训课程</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>130000510.002</t>
+          <t>14200002.009</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>130000510.004</t>
+          <t>14200002.075</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>130000510.005</t>
+          <t>14200002.076</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>130000510.006</t>
+          <t>14200002.077</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>130000510.007</t>
+          <t>14200002.078</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>130000510.008</t>
+          <t>14200002.080</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>130000510.009</t>
+          <t>14403010.001</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>国际贸易实务</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>130000510.010</t>
+          <t>15ALT016.003</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>队田径业余队</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>14200002.006</t>
+          <t>171000121.032</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>影视鉴赏</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>14200002.009</t>
+          <t>17716055.001</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>短视频平台运营与用户增长</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>14200002.075</t>
+          <t>261000011.001</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>生活中的健康管理</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>14200002.076</t>
+          <t>26100003M.006</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>“救”在你身边</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>14200002.077</t>
+          <t>61660003.001</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>音乐美学</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>14200002.078</t>
+          <t>61660003.002</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>音乐美学</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>14200002.080</t>
+          <t>61660004.002</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>音乐鉴赏</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>14403010.001</t>
+          <t>61660008.001</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>国际贸易实务</t>
+          <t>世界音乐与多元文化</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>15ALT016.003</t>
+          <t>61660009.001</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>队田径业余队</t>
+          <t>怀川弦歌：黄河文明的乐舞史诗</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>171000121.032</t>
+          <t>61660010.002</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>影视鉴赏</t>
+          <t>舞蹈鉴赏</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>17716055.001</t>
+          <t>61660011.001</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>短视频平台运营与用户增长</t>
+          <t>戏剧鉴赏</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>261000011.001</t>
+          <t>61660011.002</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>生活中的健康管理</t>
+          <t>戏剧鉴赏</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>26100003M.006</t>
+          <t>61660012.002</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>“救”在你身边</t>
+          <t>音乐的美感特征：流行中的音乐</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>61660003.001</t>
+          <t>61660012.004</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>音乐美学</t>
+          <t>音乐的美感特征：流行中的音乐</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>61660003.002</t>
+          <t>61921003.001</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>音乐美学</t>
+          <t>职场礼仪与高情商沟通</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>61660004.002</t>
+          <t>62221001.001</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>音乐鉴赏</t>
+          <t>侦探之旅：从柯南道尔到AI司鉴</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>61660008.001</t>
+          <t>62221001.002</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>世界音乐与多元文化</t>
+          <t>侦探之旅：从柯南道尔到AI司鉴</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>61660009.001</t>
+          <t>62251003.001</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>怀川弦歌：黄河文明的乐舞史诗</t>
+          <t>数字时代的感官养护</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>61660010.002</t>
+          <t>081010790.001</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>舞蹈鉴赏</t>
+          <t>高电压技术</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>61660011.001</t>
+          <t>081010810.001</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>戏剧鉴赏</t>
+          <t>现代电气控制技术与PLC</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>61660011.002</t>
+          <t>090010740.002</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>戏剧鉴赏</t>
+          <t>大数据分析技术</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>61660012.002</t>
+          <t>091010020.001</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>音乐的美感特征：流行中的音乐</t>
+          <t>算法分析与设计</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>61660012.004</t>
+          <t>091017031.001</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>音乐的美感特征：流行中的音乐</t>
+          <t>文献检索与科技论文写作</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>61921003.001</t>
+          <t>091058011.001</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>职场礼仪与高情商沟通</t>
+          <t>软件新技术讲座</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>62221001.001</t>
+          <t>110010321.001</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>侦探之旅：从柯南道尔到AI司鉴</t>
+          <t>高等代数2</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>62221001.002</t>
+          <t>150010280.001</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>侦探之旅：从柯南道尔到AI司鉴</t>
+          <t>运动处方理论与应用</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>62251003.001</t>
+          <t>150130580.002</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>数字时代的感官养护</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>081010790.001</t>
+          <t>150130580.003</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>高电压技术</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>081010810.001</t>
+          <t>150130580.004</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>现代电气控制技术与PLC</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>090010740.002</t>
+          <t>150130580.005</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>大数据分析技术</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>091010020.001</t>
+          <t>150130580.006</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>算法分析与设计</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>091017031.001</t>
+          <t>150130580.007</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>文献检索与科技论文写作</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>091058011.001</t>
+          <t>150130580.008</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>软件新技术讲座</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>110010321.001</t>
+          <t>150130680.002</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>高等代数2</t>
+          <t>专项2</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>150010280.001</t>
+          <t>150130680.003</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>运动处方理论与应用</t>
+          <t>专项2</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>150130580.002</t>
+          <t>150130680.004</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>专项2</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>150130580.003</t>
+          <t>150130680.005</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>专项2</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>150130580.004</t>
+          <t>150130680.006</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>专项2</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>150130580.005</t>
+          <t>150130700.001</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>私人教练指导</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>150130580.006</t>
+          <t>150130880.001</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>健身俱乐部经营与管理</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>150130580.007</t>
+          <t>150140220.001</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>民间武术套路2</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>150130580.008</t>
+          <t>150140470.002</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>150130680.002</t>
+          <t>150140470.003</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>150130680.003</t>
+          <t>150140470.004</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>150130680.004</t>
+          <t>150140490.002</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>150130680.005</t>
+          <t>150140490.003</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>150130680.006</t>
+          <t>150140490.004</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>150130700.001</t>
+          <t>150140570.001</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>私人教练指导</t>
+          <t>散打2</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>150130880.001</t>
+          <t>150140670.002</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>健身俱乐部经营与管理</t>
+          <t>专项3</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>150140220.001</t>
+          <t>150140670.003</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>民间武术套路2</t>
+          <t>专项3</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>150140470.002</t>
+          <t>150140670.004</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>专项3</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>150140470.003</t>
+          <t>150140760.002</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>专项5</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>150140470.004</t>
+          <t>150140760.003</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>专项5</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>150140490.002</t>
+          <t>150140760.004</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>专项5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>150140490.003</t>
+          <t>151130120.001</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>乒乓球</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>150140490.004</t>
+          <t>160060320.047</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>150140570.001</t>
+          <t>160060320.048</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>散打2</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>150140670.002</t>
+          <t>160060320.049</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>150140670.003</t>
+          <t>160060320.050</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>150140670.004</t>
+          <t>160060320.051</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>150140760.002</t>
+          <t>160060320.052</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>150140760.003</t>
+          <t>160060340.047</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>声乐6</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>150140760.004</t>
+          <t>160060340.048</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>声乐6</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>151130120.001</t>
+          <t>160060340.049</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>乒乓球</t>
+          <t>声乐6</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>160060320.047</t>
+          <t>160060340.050</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐6</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>160060320.048</t>
+          <t>160060340.051</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐6</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>160060320.049</t>
+          <t>160060360.040</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐8</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>160060320.050</t>
+          <t>160060360.041</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐8</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>160060320.051</t>
+          <t>160060360.042</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐8</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>160060320.052</t>
+          <t>160060430.001</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐艺术史及作品欣赏2</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>160060340.047</t>
+          <t>16502002.041</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>声乐6</t>
+          <t>声乐2</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>160060340.048</t>
+          <t>16502002.042</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>声乐6</t>
+          <t>声乐2</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>160060340.049</t>
+          <t>16502002.043</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>声乐6</t>
+          <t>声乐2</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>160060340.050</t>
+          <t>16502002.044</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>声乐6</t>
+          <t>声乐2</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>160060340.051</t>
+          <t>271010080.001</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>声乐6</t>
+          <t>Java EE开发技术</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>160060360.040</t>
+          <t>271010091.002</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>声乐8</t>
+          <t>移动开发技术</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>160060360.041</t>
+          <t>271030050.001</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
-        <is>
-          <t>声乐8</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>160060360.042</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>声乐8</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>160060430.001</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>声乐艺术史及作品欣赏2</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>16502002.041</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>声乐2</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>16502002.042</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>声乐2</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>16502002.043</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>声乐2</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>16502002.044</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>声乐2</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>271010080.001</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Java EE开发技术</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>271010091.002</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>移动开发技术</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>271030050.001</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
         <is>
           <t>网络编程提高</t>
         </is>

--- a/排课结果/调课失败的排课失败课程.xlsx
+++ b/排课结果/调课失败的排课失败课程.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B232"/>
+  <dimension ref="A1:B230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2459,7 +2459,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>62221001.001</t>
+          <t>62221001.002</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2471,127 +2471,127 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>62221001.002</t>
+          <t>081010790.001</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>侦探之旅：从柯南道尔到AI司鉴</t>
+          <t>高电压技术</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>62251003.001</t>
+          <t>081010810.001</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>数字时代的感官养护</t>
+          <t>现代电气控制技术与PLC</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>081010790.001</t>
+          <t>090010740.002</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>高电压技术</t>
+          <t>大数据分析技术</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>081010810.001</t>
+          <t>091010020.001</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>现代电气控制技术与PLC</t>
+          <t>算法分析与设计</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>090010740.002</t>
+          <t>091017031.001</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>大数据分析技术</t>
+          <t>文献检索与科技论文写作</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>091010020.001</t>
+          <t>091058011.001</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>算法分析与设计</t>
+          <t>软件新技术讲座</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>091017031.001</t>
+          <t>110010321.001</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>文献检索与科技论文写作</t>
+          <t>高等代数2</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>091058011.001</t>
+          <t>150010280.001</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>软件新技术讲座</t>
+          <t>运动处方理论与应用</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>110010321.001</t>
+          <t>150130580.002</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>高等代数2</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>150010280.001</t>
+          <t>150130580.003</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>运动处方理论与应用</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>150130580.002</t>
+          <t>150130580.004</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -2603,7 +2603,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>150130580.003</t>
+          <t>150130580.005</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -2615,7 +2615,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>150130580.004</t>
+          <t>150130580.006</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -2627,7 +2627,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>150130580.005</t>
+          <t>150130580.007</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>150130580.006</t>
+          <t>150130580.008</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -2651,31 +2651,31 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>150130580.007</t>
+          <t>150130680.002</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>专项2</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>150130580.008</t>
+          <t>150130680.003</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>专项2</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>150130680.002</t>
+          <t>150130680.004</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -2687,7 +2687,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>150130680.003</t>
+          <t>150130680.005</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -2699,7 +2699,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>150130680.004</t>
+          <t>150130680.006</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -2711,67 +2711,67 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>150130680.005</t>
+          <t>150130700.001</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>私人教练指导</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>150130680.006</t>
+          <t>150130880.001</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>健身俱乐部经营与管理</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>150130700.001</t>
+          <t>150140220.001</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>私人教练指导</t>
+          <t>民间武术套路2</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>150130880.001</t>
+          <t>150140470.002</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>健身俱乐部经营与管理</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>150140220.001</t>
+          <t>150140470.003</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>民间武术套路2</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>150140470.002</t>
+          <t>150140470.004</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -2783,31 +2783,31 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>150140470.003</t>
+          <t>150140490.002</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>150140470.004</t>
+          <t>150140490.003</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>150140490.002</t>
+          <t>150140490.004</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -2819,43 +2819,43 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>150140490.003</t>
+          <t>150140570.001</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>散打2</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>150140490.004</t>
+          <t>150140670.002</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>专项3</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>150140570.001</t>
+          <t>150140670.003</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>散打2</t>
+          <t>专项3</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>150140670.002</t>
+          <t>150140670.004</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -2867,31 +2867,31 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>150140670.003</t>
+          <t>150140760.002</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>专项5</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>150140670.004</t>
+          <t>150140760.003</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>专项5</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>150140760.002</t>
+          <t>150140760.004</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -2903,43 +2903,43 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>150140760.003</t>
+          <t>151130120.001</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>乒乓球</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>150140760.004</t>
+          <t>160060320.047</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>151130120.001</t>
+          <t>160060320.048</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>乒乓球</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>160060320.047</t>
+          <t>160060320.049</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -2951,7 +2951,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>160060320.048</t>
+          <t>160060320.050</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -2963,7 +2963,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>160060320.049</t>
+          <t>160060320.051</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>160060320.050</t>
+          <t>160060320.052</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -2987,31 +2987,31 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>160060320.051</t>
+          <t>160060340.047</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐6</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>160060320.052</t>
+          <t>160060340.048</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐6</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>160060340.047</t>
+          <t>160060340.049</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>160060340.048</t>
+          <t>160060340.050</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>160060340.049</t>
+          <t>160060340.051</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3047,31 +3047,31 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>160060340.050</t>
+          <t>160060360.040</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>声乐6</t>
+          <t>声乐8</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>160060340.051</t>
+          <t>160060360.041</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>声乐6</t>
+          <t>声乐8</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>160060360.040</t>
+          <t>160060360.042</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3083,43 +3083,43 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>160060360.041</t>
+          <t>160060430.001</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>声乐8</t>
+          <t>声乐艺术史及作品欣赏2</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>160060360.042</t>
+          <t>16502002.041</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>声乐8</t>
+          <t>声乐2</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>160060430.001</t>
+          <t>16502002.042</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>声乐艺术史及作品欣赏2</t>
+          <t>声乐2</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>16502002.041</t>
+          <t>16502002.043</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3131,7 +3131,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>16502002.042</t>
+          <t>16502002.044</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3143,58 +3143,34 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>16502002.043</t>
+          <t>271010080.001</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>声乐2</t>
+          <t>Java EE开发技术</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>16502002.044</t>
+          <t>271010091.002</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>声乐2</t>
+          <t>移动开发技术</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>271010080.001</t>
+          <t>271030050.001</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
-        <is>
-          <t>Java EE开发技术</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>271010091.002</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>移动开发技术</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>271030050.001</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
         <is>
           <t>网络编程提高</t>
         </is>
